--- a/ABC突破切線圖表_20260615/ABC突破切線精選_20260615.xlsx
+++ b/ABC突破切線圖表_20260615/ABC突破切線精選_20260615.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -557,30 +557,30 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3311.TW</t>
+          <t>8261.TW</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>41.3</v>
+        <v>173.5</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>39.75</v>
+        <v>163.33</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3901</v>
+        <v>13685</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -591,30 +591,30 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>6191.TW</t>
+          <t>3014.TW</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>97.58</v>
+        <v>151.75</v>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>21329</v>
+        <v>4591</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
@@ -625,30 +625,30 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>5392.TWO</t>
+          <t>8088.TWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>能率</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>44.9</v>
+        <v>61.4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>44.9</v>
+        <v>59</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6957</v>
+        <v>4121</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
@@ -659,30 +659,30 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>8255.TWO</t>
+          <t>3264.TWO</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>朋程</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>183</v>
+        <v>227.5</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>166.5</v>
+        <v>222.25</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>9.91%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>4232</v>
+        <v>9120</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -693,30 +693,30 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3413.TW</t>
+          <t>1342.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>322</v>
+        <v>117.5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>310.5</v>
+        <v>109.5</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.31%</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4562</v>
+        <v>2096</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -727,30 +727,30 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>9933.TW</t>
+          <t>1608.TW</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>中鼎</t>
+          <t>華榮</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>42.8</v>
+        <v>34.4</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>41.93</v>
+        <v>32.82</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>4.81%</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>8074</v>
+        <v>5673</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -761,30 +761,30 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3234.TWO</t>
+          <t>2641.TWO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>正德</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>122.5</v>
+        <v>18.8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>121</v>
+        <v>18.5</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2834</v>
+        <v>2913</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
@@ -795,30 +795,30 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>53.9</v>
+        <v>18</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>53</v>
+        <v>17.66</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10131</v>
+        <v>8916</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -829,30 +829,30 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1563.TW</t>
+          <t>6257.TW</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>64</v>
+        <v>221.5</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>59.2</v>
+        <v>208.5</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>8.11%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1147</v>
+        <v>8987</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -863,27 +863,27 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>2302.TW</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>麗正</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4470</v>
+        <v>34.65</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4396.25</v>
+        <v>31.29</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>10.75%</t>
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11647</v>
+        <v>1715</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>1.5</v>
@@ -897,30 +897,30 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2441.TW</t>
+          <t>6139.TW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>127</v>
+        <v>805</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>122.4</v>
+        <v>761.67</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>9334</v>
+        <v>5499</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
@@ -931,30 +931,30 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>3149.TW</t>
+          <t>2601.TW</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>正達</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>87.40000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>86.88</v>
+        <v>5.66</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4165</v>
+        <v>1788</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -965,30 +965,30 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2369.TW</t>
+          <t>5864.TWO</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>菱生</t>
+          <t>致和證</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>35.75</v>
+        <v>47.2</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>35.4</v>
+        <v>40.77</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>15.78%</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>14276</v>
+        <v>8930</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
@@ -999,27 +999,27 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>2405.TW</t>
+          <t>2323.TW</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>輔信</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>19.45</v>
+        <v>11.2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>19.32</v>
+        <v>11</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4285</v>
+        <v>9946</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>1.1</v>
@@ -1033,134 +1033,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>960</v>
+        <v>18.9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>934</v>
+        <v>18.85</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16532</v>
+        <v>57479</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>3450.TW</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>507</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>483.6</v>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>4.84%</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>5448</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>3289.TWO</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>宜特</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>164.17</v>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2.94%</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>1947</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>6548.TWO</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>長科*</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>5.0%</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>2846</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1183,9 +1081,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
